--- a/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Forest/Forest_CrossTabs_CadreDivide.xlsx
+++ b/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Forest/Forest_CrossTabs_CadreDivide.xlsx
@@ -672,27 +672,27 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3.28</v>
+        <v>4.59</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.49</v>
+        <v>4.5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3.24</v>
+        <v>4.88</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.89</v>
+        <v>1.12</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.88</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
@@ -702,27 +702,27 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="6">
@@ -732,27 +732,27 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -762,27 +762,27 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
